--- a/reports/sampling_records.xlsx
+++ b/reports/sampling_records.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -940,6 +940,56 @@
         <v>119.3152868747711</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>\Users\BARIS\Documents\GitHub\DiffuVQA\checkpoints\btch4\lr0.0001\ema_0.9999_001000.pt</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>123</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G21" t="n">
+        <v>444.6722791194916</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>\Users\BARIS\Documents\GitHub\DiffuVQA\checkpoints\btch4\lr0.0001\ema_0.9999_001000.pt</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>123</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G22" t="n">
+        <v>499.2227303981781</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
